--- a/StructureDefinition-inera-ehds-audit-event-patient-read.xlsx
+++ b/StructureDefinition-inera-ehds-audit-event-patient-read.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
